--- a/Seep-Logos-agents/marketing/sns/templates/game-launch-templates.xlsx
+++ b/Seep-Logos-agents/marketing/sns/templates/game-launch-templates.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -481,11 +481,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新作ゲーム X投稿テンプレート集（汎用版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
+          <t>新作ゲーム X投稿テンプレート集（汎用版）全71パターン</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>フェーズ</t>
@@ -1170,6 +1170,1197 @@
 詳細は公式サイトをご確認ください▼
 [公式サイトURL]
 [ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（単体）</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>A：シンプルキャラ紹介型</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』に登場するキャラクターをご紹介します！
+[キャラクター名]（CV：[声優名]）
+[キャラクターの一言紹介文]
+▼詳細は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（単体）</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>B：ビジュアル公開連動型</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』キャラクタービジュアルを公開しました！
+[キャラクター名]（CV：[声優名]）
+▼詳細は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ] #[作品タイトル]キャラクター</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（単体）</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>C：キャラクター設定公開型</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>【キャラクター情報】
+『[作品タイトル]』登場キャラクター、[キャラクター名]の情報を公開しました。
+[キャラクターの属性・役割等を1行で]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（複数）</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>A：キャラクター一覧公開型</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』の登場キャラクター情報を更新しました！
+[キャラクター名]／[キャラクター名]／[キャラクター名]
+▼キャラクター一覧はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（複数）</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>B：グループ・パーティ紹介型</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[グループ名]のメンバーを一挙公開！
+[キャラクター名]：[声優名]
+[キャラクター名]：[声優名]
+[キャラクター名]：[声優名]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>A：コラボ発表型（スタンダード）</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>【コラボ情報】
+『[作品タイトル]』×『[コラボ作品名]』コラボレーションの実施が決定しました！
+■開催期間：[開始日]〜[終了日]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ] #[コラボ作品名]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Phase 7：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>B：コラボ開始告知型</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>【コラボ開催中！】
+『[作品タイトル]』×『[コラボ作品名]』コラボイベントが本日よりスタートしました！
+■期間：[開始日]〜[終了日]
+■内容：[概要]
+詳細はこちら▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Phase 7：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>C：コラボ終了間近告知型</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』×『[コラボ作品名]』コラボイベントは[終了日]（[曜日]）までです！
+お見逃しなく！
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Phase 7：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>D：コラボ終了報告型</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』×『[コラボ作品名]』コラボイベントが終了しました。
+ご参加いただいた皆さん、ありがとうございました！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>アップデート告知</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>A：バージョンアップ告知型</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>【アップデートのお知らせ】
+[日付]（[曜日]）にVer.[X.X]へのアップデートを実施します。
+■主な更新内容：
+・[内容1]
+・[内容2]
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>アップデート告知</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>B：新コンテンツ追加告知型</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>【新コンテンツ追加！】
+[日付]（[曜日]）のアップデートで[コンテンツ名]が追加されます！
+[概要を1〜2文で]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>アップデート告知</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>C：アップデート完了報告型</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>アップデートが完了しました。ご不便をおかけし、申し訳ございませんでした。
+引き続き『[作品タイトル]』をお楽しみください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>メンテナンス告知</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>A：メンテナンス予告型</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>【メンテナンスのお知らせ】
+[日付]（[曜日]）[開始時刻]〜[終了時刻]（予定）にメンテナンスを実施します。
+■対象：[対象の説明]
+ご迷惑をおかけしますが、よろしくお願いいたします。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>メンテナンス告知</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>B：メンテナンス開始告知型</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>【メンテナンス開始】
+ただいよりメンテナンスを開始いたしました。
+終了まで今しばらくお待ちください。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>メンテナンス告知</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>C：メンテナンス終了告知型</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>【メンテナンス終了】
+メンテナンスが完了しました。
+ご不便をおかけし、申し訳ございませんでした。
+引き続き『[作品タイトル]』をお楽しみください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>不具合・お詫び</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>A：不具合報告型</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>【不具合のお知らせ】
+現在、[不具合の内容]が発生しております。
+ご不便をおかけし、誠に申し訳ございません。
+対応が完了次第、改めてお知らせいたします。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：アップデート・メンテナンス</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>不具合・お詫び</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>B：不具合修正完了型</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>先ほどご報告しました[不具合の内容]につきまして、修正が完了しました。
+ご迷惑をおかけし、大変申し訳ございませんでした。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Phase 9：ランキング・実績報告</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>DL数・ランキング報告</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>A：DL数達成型</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』、おかげさまで[X]万ダウンロードを突破しました！
+皆さんのご支援に心より感謝いたします。
+今後ともよろしくお願いいたします。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Phase 9：ランキング・実績報告</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>DL数・ランキング報告</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>B：ランキング1位報告型</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』が[ストア名]ランキング[カテゴリ]部門で1位を獲得しました！
+ご支援いただいた皆さん、ありがとうございます！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Phase 9：ランキング・実績報告</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>DL数・ランキング報告</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>C：売上・ユーザー数報告型</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』の登録ユーザー数が[X]万人を突破しました！
+たくさんのご支援、ありがとうございます。
+引き続きよろしくお願いいたします。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Phase 10：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>サービス周年</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>A：X周年告知型（スタンダード）</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』はおかげさまで本日[X]周年を迎えました！
+いつも応援していただき、ありがとうございます。
+今後ともよろしくお願いいたします。
+[ハッシュタグ] #[作品タイトル][X]周年</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>サービス周年</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>B：周年イベント告知型</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>【[X]周年記念イベント開催！】
+『[作品タイトル]』[X]周年を記念して特別イベントを開催します！
+■期間：[開始日]〜[終了日]
+■内容：[概要]
+詳細はこちら▼
+[公式サイトURL]
+[ハッシュタグ] #[作品タイトル][X]周年</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>サービス周年</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>C：周年お礼メッセージ型</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>本日、『[作品タイトル]』は[X]周年を迎えました。
+ここまで続けてこられたのは、プレイしてくださっている皆さんのおかげです。
+これからも応援よろしくお願いいたします！
+[ハッシュタグ] #[作品タイトル][X]周年</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Phase 11：シーズナルイベント</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>季節イベント告知</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>A：イベント開始告知型</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>【[イベント名]開催中！】
+[X]月[X]日（[曜日]）より[イベント名]を開催しています！
+[イベント概要を1〜2文で]
+詳細はこちら▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：シーズナルイベント</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>季節イベント告知</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>B：イベント終了間近型</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[イベント名]は[終了日]（[曜日]）[時刻]に終了します！
+まだ参加されていない方はお早めに！
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：シーズナルイベント</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>季節イベント告知</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>C：特別ログインボーナス告知型</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>【ログインボーナス開催中！】
+[期間]の期間中、毎日ログインで特別アイテムをプレゼント！
+[概要を1文で]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：シーズナルイベント</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>ガチャ・召喚告知</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>A：新ガチャ開始告知型</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>【新ガチャ登場！】
+[X]月[X]日（[曜日]）より[ガチャ名]を開催します！
+[ピックアップキャラ・アイテム名]が期間限定で登場！
+■期間：[開始日]〜[終了日]
+詳細はこちら▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：シーズナルイベント</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>ガチャ・召喚告知</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>B：ガチャ終了間近告知型</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>『[ガチャ名]』は[終了日]（[曜日]）[時刻]に終了します！
+[ピックアップキャラ名]を獲得するチャンスはお早めに！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Phase 12：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>A：新グッズ発表型</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>【グッズ情報】
+『[作品タイトル]』[グッズ名]の発売が決定しました！
+■発売日：[発売日]
+■価格：[価格]
+■取扱：[販売店/通販サイト]
+詳細はこちら▼
+[URL]
+[ハッシュタグ] #[作品タイトル]グッズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Phase 12：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>B：予約開始告知型</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[グッズ名]の予約受付を開始しました！
+■予約締切：[締切日]
+■発売予定：[発売日]
+▼予約はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Phase 12：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>C：コラボカフェ・ポップアップ告知型</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>【コラボカフェ開催決定！】
+『[作品タイトル]』コラボカフェを[場所]にて開催します！
+■期間：[開始日]〜[終了日]
+■場所：[会場名・住所]
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Phase 13：生放送・公式配信</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>生放送告知</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>A：生放送予告型</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>【生放送のお知らせ】
+[日付]（[曜日]）[時刻]より公式生放送を配信します！
+■内容：[放送内容の概要]
+▼視聴はこちら
+[配信URL]
+[ハッシュタグ] #[作品タイトル]生放送</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Phase 13：生放送・公式配信</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>生放送告知</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>B：生放送開始告知型</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>【生放送スタート！】
+ただいまより公式生放送を開始しました！
+▼こちらからご覧いただけます
+[配信URL]
+[ハッシュタグ] #[作品タイトル]生放送</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Phase 13：生放送・公式配信</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>生放送告知</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>C：生放送終了報告型</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>公式生放送をご視聴いただきありがとうございました！
+アーカイブはこちらからご覧いただけます▼
+[配信URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Phase 14：メディア掲載・受賞</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>メディア掲載報告</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>A：メディア掲載報告型</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』が[メディア名]に掲載されました！
+▼記事はこちら
+[記事URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Phase 14：メディア掲載・受賞</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>受賞報告</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>A：受賞報告型</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』が[賞の名称]を受賞しました！
+応援していただいた皆さん、ありがとうございます！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Phase 14：メディア掲載・受賞</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>受賞報告</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>B：ノミネート報告型</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』が[賞の名称]にノミネートされました！
+引き続き応援よろしくお願いいたします！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Phase 15：重要告知</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>サービス情報変更</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>A：料金・仕様変更告知型</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>【重要なお知らせ】
+[日付]より[変更内容]を変更いたします。
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Phase 15：重要告知</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>サービス情報変更</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>B：利用規約改定告知型</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>【利用規約改定のお知らせ】
+[日付]より利用規約を改定いたします。
+詳細はこちらをご確認ください▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>A：問いかけ型</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>皆さんは『[作品タイトル]』でどのキャラクターが好きですか？
+#[ハッシュタグ] でコメントを教えてください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>B：イラスト・ファンアート紹介型</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>素敵なファンアートをご紹介します！
+[ハッシュタグ]をつけて投稿いただいた作品です。
+いつも応援ありがとうございます！
+[ハッシュタグ] #[作品タイトル]ファンアート</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>C：公式サイト・SNS誘導型</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』の最新情報は公式アカウントとサイトをチェック！
+▼公式サイト
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>D：フォロワー感謝型</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>公式アカウントのフォロワーが[X]万人を突破しました！
+いつもご支援いただきありがとうございます。
+引き続きよろしくお願いいたします！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>E：壁紙・特典配布型</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』公式壁紙を無料配布中！
+▼ダウンロードはこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>情報まとめ投稿</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>A：週間まとめ型</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>今週の『[作品タイトル]』情報をまとめました！
+・[情報1]
+・[情報2]
+・[情報3]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>情報まとめ投稿</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>B：初心者向け案内型</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』をはじめて知った方へ！
+[タイトルの概要を2〜3文で]
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ] #新作ゲーム</t>
         </is>
       </c>
     </row>

--- a/Seep-Logos-agents/marketing/sns/templates/game-launch-templates.xlsx
+++ b/Seep-Logos-agents/marketing/sns/templates/game-launch-templates.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,18 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +67,63 @@
         <fgColor rgb="00F9F9F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCF3CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDFEFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -80,11 +145,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -104,6 +213,47 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -481,7 +631,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新作ゲーム X投稿テンプレート集（汎用版）全71パターン</t>
+          <t>新作ゲーム X投稿テンプレート集（汎用版）全107パターン</t>
         </is>
       </c>
     </row>
@@ -2361,6 +2511,941 @@
 ▼詳細はこちら
 [公式サイトURL]
 [ハッシュタグ] #新作ゲーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>体験版・デモ公開</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>A：体験版公開告知型</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』体験版を公開しました！
+▼ダウンロードはこちら
+App Store：[URL]
+Google Play：[URL]
+製品版は[発売時期]発売予定。ぜひお試しください！
+[ハッシュタグ] #新作ゲーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>体験版・デモ公開</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>B：体験版期間告知型</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』体験版を[開始日]より配信開始します！
+■対象プラットフォーム：[プラットフォーム]
+■体験版配信期間：[開始日]〜[終了日]
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>体験版・デモ公開</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>C：体験版終了間近型</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』体験版の配信は[終了日]（[曜日]）までです！
+まだプレイしていない方はお早めに！
+▼ダウンロードはこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>ゲームプレイ動画公開</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>A：ゲームプレイ動画公開型</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』のゲームプレイ映像を公開しました！
+▼ゲームプレイ映像はこちら
+[動画URL]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ] #新作ゲーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>ゲームプレイ動画公開</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>B：スクリーンショット公開型</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』のゲーム内スクリーンショットを公開しました！
+[システムやシーンの一言説明]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>ゲームシステム詳細紹介</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>A：バトルシステム紹介型</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>【バトルシステム紹介】
+『[作品タイトル]』のバトルシステムをご紹介します！
+[バトルシステムの概要を1〜2文で]
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>ゲームシステム詳細紹介</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>B：新機能追加告知型</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>【新機能追加！】
+アップデートにて[機能名]が追加されます！
+[機能の概要を1〜2文で]
+■アップデート予定日：[日付]
+詳細はこちら▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：ゲームシステム紹介（詳細版）</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>ゲームシステム詳細紹介</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>C：機能アップデート完了型</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>【機能アップデート完了】
+[機能名]のアップデートが完了しました！
+[変更内容を1〜2文で]
+ぜひお試しください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Phase 18：期間・カウントダウン</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>カウントダウン告知</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>A：残りX日型（シンプル）</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』発売まであと[X]日！
+▼詳細・予約はこちら
+[公式サイトURL]
+[ハッシュタグ] #新作ゲーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：期間・カウントダウン</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>カウントダウン告知</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>B：残りX日型（情報添付）</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』リリースまであと[X]日！
+[ジャンル] | [プラットフォーム]
+▼事前登録・詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：期間・カウントダウン</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>カウントダウン告知</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>C：残りX日型（キャンペーン連動）</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』リリースまであと[X]日！
+事前登録はお済みですか？特典として[特典内容]をプレゼント中！
+▼事前登録はこちら
+[登録URL]
+[ハッシュタグ] #事前登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：期間・カウントダウン</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>期間終了間近</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>A：イベント終了間近型</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[イベント名]は[終了日]（[曜日]）[時刻]に終了します！
+まだ参加されていない方はお早めに！
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：期間・カウントダウン</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>期間終了間近</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>B：キャンペーン終了間近型</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>【キャンペーン終了間近！】
+[キャンペーン名]は[終了日]（[曜日]）[時刻]に終了します！
+まだ応募されていない方はお急ぎください！
+▼応募はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：期間・カウントダウン</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>期間終了間近</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>C：予約・販売終了間近型</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[商品名]の予約締切は[締切日]（[曜日]）です！
+ご検討中の方はお早めに！
+▼予約はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Phase 19：ガチャ・ログインボーナス</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>ガチャ・召喚（詳細版）</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>A：新ガチャ開始（ピックアップ明記型）</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>【新ガチャ登場！】
+[X]月[X]日（[曜日]）[時刻]より[ガチャ名]を開催します！
+ピックアップ：[キャラクター/アイテム名]
+■期間：[開始日]〜[終了日]
+■レアリティ：[内容]
+詳細はこちら▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：ガチャ・ログインボーナス</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>ガチャ・召喚（詳細版）</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>B：ガチャ終了間近型</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>『[ガチャ名]』は[終了日]（[曜日]）[時刻]に終了します！
+[ピックアップキャラ/アイテム名]の獲得はお早めに！
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：ガチャ・ログインボーナス</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>ガチャ・召喚（詳細版）</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>C：ガチャ終了報告型</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>『[ガチャ名]』は終了しました。
+ご参加いただいた皆さん、ありがとうございました！
+次回の開催をお楽しみに！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：ガチャ・ログインボーナス</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>ログインボーナス</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>A：ログインボーナス開始型</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>【ログインボーナス開催中！】
+[X]月[X]日（[曜日]）〜[終了日]（[曜日]）の期間中、毎日ログインで特別アイテムをプレゼント！
+[特典内容の概要]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：ガチャ・ログインボーナス</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>ログインボーナス</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>B：ログインボーナス終了間近型</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>ログインボーナスは[終了日]（[曜日]）で終了します！
+まだ受け取っていない方はお早めに！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Phase 20：告知・お知らせ（詳細版）</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>重要告知</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>A：サービス・仕様変更告知型</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>【重要なお知らせ】
+[日付]（[曜日]）より[変更内容]を変更いたします。
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：告知・お知らせ（詳細版）</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>重要告知</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>B：緊急告知・障害報告型</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>【緊急のお知らせ】
+現在、[発生している問題]が発生しており、ご不便をおかけしております。
+対応中のため、今しばらくお待ちください。
+進捗については随時こちらでお知らせいたします。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：告知・お知らせ（詳細版）</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>重要告知</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>C：対応完了報告型</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>先ほどお知らせいたしました[問題内容]につきまして、対応が完了しました。
+ご不便・ご迷惑をおかけし、誠に申し訳ございませんでした。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：告知・お知らせ（詳細版）</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>価格・規約変更</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>A：利用規約改定告知型</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>【利用規約改定のお知らせ】
+[日付]（[曜日]）より利用規約を改定いたします。
+詳細はこちらをご確認ください▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>アンケート投稿</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>A：推しキャラ問いかけ型</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>皆さんに質問です！
+『[作品タイトル]』で一番好きなキャラクターは誰ですか？
+コメントで教えてください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>アンケート投稿</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>B：プレイスタイル問いかけ型</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>皆さんはどんなプレイスタイルで楽しんでいますか？
+[質問内容（例：ストーリー重視 / バトル重視）]
+#[ハッシュタグ]でコメントをお聞かせください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>アンケート投稿</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>C：感想収集型</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』最新アップデートはいかがでしたか？
+ご意見・ご感想を[ハッシュタグ]で教えてください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>壁紙・素材配布</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>A：壁紙配布告知型</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』の公式壁紙を[X]種類配布中！
+▼ダウンロードはこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>壁紙・素材配布</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>B：SNS用アイコン配布型</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』公式SNSアイコン素材を配布中！
+ぜひご活用ください！
+▼ダウンロードはこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>ファンアート・UGC紹介</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>A：ファンアート紹介型</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>素敵なファンアートをご紹介します！
+[ハッシュタグ]をつけて投稿いただいた作品です。
+いつも応援ありがとうございます！
+[ハッシュタグ] #[作品タイトル]ファンアート</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>ファンアート・UGC紹介</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>B：ファンアート募集型</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』のファンアート募集中！
+[ハッシュタグ]をつけてXに投稿してください。
+公式アカウントでご紹介させていただくことがあります！
+[ハッシュタグ] #[作品タイトル]ファンアート</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>フォロワー感謝</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>A：フォロワー達成感謝型</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>公式アカウントのフォロワーが[X]万人を突破しました！
+いつも応援いただきありがとうございます。
+引き続き最新情報をお届けしますので、よろしくお願いいたします！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>週次情報まとめ</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>A：週間情報まとめ型</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>今週の『[作品タイトル]』情報をまとめました！
+・[情報1]
+・[情報2]
+・[情報3]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>週次情報まとめ</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>B：初心者向け案内型</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>はじめて『[作品タイトル]』を知った方へ！
+[タイトルの概要を2〜3文で]
+▼詳細はこちら
+[公式サイトURL]
+[ハッシュタグ] #新作ゲーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Phase 22：事前登録（詳細版）</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>事前登録促進</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>A：特典強調型</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』事前登録受付中！
+事前登録者全員に[特典内容]をプレゼント！
+[発売時期]配信予定。まだ登録がお済みでない方はぜひ！
+▼事前登録はこちら
+[登録URL]
+[ハッシュタグ] #事前登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：事前登録（詳細版）</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>事前登録促進</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>B：締切直前告知型</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』事前登録は[終了日]（[曜日]）までです！
+まだ登録がお済みでない方はお早めに！
+▼事前登録はこちら
+[登録URL]
+[ハッシュタグ] #事前登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：事前登録（詳細版）</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>事前登録促進</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>C：目標達成感謝＋次目標型</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』事前登録者数[X]万人を達成しました！
+ありがとうございます！
+次の目標は[次の目標数]万人です。引き続きよろしくお願いいたします！
+▼事前登録はこちら
+[登録URL]
+[ハッシュタグ] #事前登録</t>
         </is>
       </c>
     </row>
@@ -2378,383 +3463,2083 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>よく使われる定型フレーズ一覧（ゲーム向け）</t>
-        </is>
-      </c>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>よく使われる定型フレーズ一覧（ゲーム向け）（全136フレーズ）</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>フレーズ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>「情報解禁！」「情報解禁しました」</t>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>「情報解禁！」</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>「ティザーサイトを公開しました」「公式サイトを公開しました」</t>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>「情報解禁しました」</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>「PVを公開しました」「ティザーPVを公開しました」</t>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>「本日、情報を解禁いたします」</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>「ティザービジュアルを公開しました」「キービジュアルを公開しました」</t>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>「ティザーサイトを公開しました」</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>「公式サイトをオープンしました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>「公式サイトをリニューアルしました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>「PVを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>「ティザーPVを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>「PV第[X]弾を公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>「ローンチトレーラーを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>「ティザービジュアルを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>「キービジュアルを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>「キービジュアル第[X]弾を公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>「本日より〇〇を公開しています」</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>「スクリーンショットを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>「ゲームプレイ映像を公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>告知・お知らせ系</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>「〇〇の開発・発売が決定しました」</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>告知・お知らせ系</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>「〇〇についてお知らせいたします」</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>告知・お知らせ系</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>「〇〇を発表いたします」</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>告知・お知らせ系</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>「新作ゲーム『[作品タイトル]』の発売が決定いたしました」</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>告知・お知らせ系</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>「新作ゲーム『[作品タイトル]』を発表いたします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>告知・お知らせ系</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>「【お知らせ】〇〇が決定しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>告知・お知らせ系</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>「【発表】〇〇のご案内」</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>告知・お知らせ系</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>「重要なお知らせがあります」</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>告知・お知らせ系</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>「大切なお知らせです」</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>期日・日程明示系</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>「[発売時期]発売予定」</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>期日・日程明示系</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>「本日より」「本日[発売時期]よりサービス開始」</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>「[発売時期]リリース予定」</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>期日・日程明示系</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>「本日より」</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>期日・日程明示系</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>「本日[発売時期]よりサービス開始」</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>期日・日程明示系</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>「[日付]（[曜日]）[時刻]より」</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>期日・日程明示系</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>「[日付]リリース予定」</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>期日・日程明示系</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>「[日付]より受付開始」</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>期日・日程明示系</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>「[日付]（[曜日]）まで」</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>期日・日程明示系</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>「〇〇は[終了日]に終了します」</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>期日・日程明示系</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>「残り[X]日！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>事前登録・キャンペーン系</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>「事前登録受付中！」「事前登録受付中です」</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>「事前登録受付中！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>事前登録・キャンペーン系</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>「事前登録を開始しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>事前登録・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>「事前登録受付中です」</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>事前登録・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>「事前登録者数[X]万人突破！」</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>事前登録・キャンペーン系</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>「事前登録者数が[X]万人を突破しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>事前登録・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>「事前登録特典として〇〇をプレゼント」</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>事前登録・キャンペーン系</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>「事前登録はこちら▼」</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>事前登録・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>「登録はお済みですか？」</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>事前登録・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>「まだ登録がお済みでない方はお早めに」</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>リリース・サービス開始系</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>「本日サービス開始！」「本日より配信スタートです！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>「本日サービス開始！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>リリース・サービス開始系</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>「ついにリリース！」「本日ついにリリースとなりました！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>「本日より配信スタートです！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>リリース・サービス開始系</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>「ついにリリース！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>「本日ついにリリースとなりました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>「本日、〇〇の発売日を迎えました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>「App Store・Google Playにて配信中！」</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>リリース・サービス開始系</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>「ダウンロードはこちら▼」「今すぐプレイ▼」</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>「[プラットフォーム]にて発売中です」</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>「ダウンロードはこちら▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>「今すぐプレイ▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>「予約受付中！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>「予約はこちら▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>リリース・サービス開始系</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>「購入・ダウンロードはこちら▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>「多くの方にご支援・ご声援をいただき、ありがとうございます」</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>「おかげさまで事前登録者数[X]万人を達成しました」</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>「たくさんのご反響をいただきありがとうございます」</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>「引き続きよろしくお願いいたします」</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>「今後ともよろしくお願いいたします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>「いつも応援いただきありがとうございます」</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>「皆さんのご支援に心より感謝いたします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>「リリースから[X]日、[X]万ダウンロードを達成しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>「おかげさまで[X]万ダウンロードを突破しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>「[ストア名]ランキング[カテゴリ]部門で1位を獲得しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>「登録ユーザー数が[X]万人を突破しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>「続報をお待ちください」「続報は公式アカウントでお知らせします」</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>「続報をお待ちください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>「続報は公式アカウントでお知らせします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>「詳細は公式サイトをご確認ください▼」</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>「フォローして最新情報をチェック！」</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>「次回の情報公開をお楽しみに！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>「続報は近日公開予定です」</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>「近日中に詳細をお知らせします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>「最新情報は公式アカウントでご確認ください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>「キャラクター情報を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>「キャスト情報を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>「キャラクタービジュアルを公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>「[キャラクター名]（CV：[声優名]）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>「[キャラクター名]役を[声優名]さんが担当します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>「[キャラクター名]のプロフィールを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>キャラクター紹介系</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>「キャラクター一覧は公式サイトをご確認ください▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>「ゲームシステムをご紹介します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>「ゲームの特徴をご紹介します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>「新機能を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>「[機能名]の詳細はこちら▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>「ゲームプレイ動画を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>「体験版・デモ版を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>ゲームシステム紹介系</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>「体験版のダウンロードはこちら▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>「【アップデートのお知らせ】」</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>「【メンテナンスのお知らせ】」</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>「Ver.[X.X]へのアップデートを実施します」</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>「[日付]（[曜日]）[開始時刻]〜[終了時刻]（予定）にメンテナンスを実施します」</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>「ただいよりメンテナンスを開始いたしました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>「メンテナンスが完了しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>「アップデートが完了しました。ご不便をおかけし、申し訳ございませんでした」</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>「【不具合のお知らせ】現在、[不具合の内容]が発生しております」</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>「不具合の修正が完了しました。ご迷惑をおかけし、誠に申し訳ございませんでした」</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>アップデート・メンテナンス系</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>「ご不便をおかけし、申し訳ございません。対応が完了次第、改めてお知らせいたします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>「【キャンペーン開催中！】」</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>「【期間限定イベント開催中！】」</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>「フォロー＆リツイートで[賞品]が当たる！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>「①[@公式アカウント]をフォロー ②この投稿をリツイート」</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>「■応募期間：[開始日]〜[終了日]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>「■当選数：[X]名」</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="n">
+        <v>106</v>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>「[イベント名]は[終了日]までです！お見逃しなく！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>「ログインボーナム開催中！毎日ログインで特別アイテムをプレゼント！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="18" t="n">
+        <v>108</v>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>イベント・キャンペーン系</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>「[ガチャ名]は[終了日]に終了します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>「【コラボ情報】〇〇×〇〇コラボレーション決定！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>「〇〇×〇〇コラボイベントが本日よりスタートしました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="19" t="n">
+        <v>111</v>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="inlineStr">
+        <is>
+          <t>「コラボイベントは[終了日]（[曜日]）までです！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="19" t="n">
+        <v>112</v>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>「コラボイベントが終了しました。ご参加いただいた皆さん、ありがとうございました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>周年・記念系</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>「おかげさまで本日[X]周年を迎えました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>周年・記念系</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>「[X]周年を記念して特別イベントを開催します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>周年・記念系</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>「[X]周年、いつも応援していただきありがとうございます」</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>周年・記念系</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>「本日は[キャラクター名]の誕生日です！お誕生日おめでとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>グッズ・商品系</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>「【グッズ情報】〇〇の発売が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>グッズ・商品系</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>「予約受付を開始しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>グッズ・商品系</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>「■発売日：[発売日] ■価格：[価格]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>グッズ・商品系</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>「▼予約はこちら [URL]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>グッズ・商品系</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>「コラボカフェを[場所]にて開催します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>122</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>生放送・配信系</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>「【生放送のお知らせ】[日付]（[曜日]）[時刻]より公式生放送を配信します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>123</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>生放送・配信系</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>「ただいまより公式生放送を開始しました！▼こちらからご覧いただけます」</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>生放送・配信系</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>「公式生放送をご視聴いただきありがとうございました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>生放送・配信系</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>「アーカイブはこちらからご覧いただけます▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>「[賞の名称]を受賞しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>「[賞の名称]にノミネートされました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>「[メディア名]に掲載されました！▼記事はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="n">
+        <v>129</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>「応援していただいた皆さんのおかげです。ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>「皆さんは[作品タイトル]でどのキャラクターが好きですか？」</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="n">
+        <v>131</v>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>「#[ハッシュタグ]でコメントを教えてください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>「素敵なファンアートをご紹介します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>「いつも応援ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>「公式壁紙を無料配布中！▼ダウンロードはこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>「フォロワーが[X]万人を突破しました！ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>「最新情報は公式サイト・公式アカウントをチェック！」</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
